--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -441,12 +441,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
     </row>
@@ -458,12 +458,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
     </row>
@@ -475,12 +475,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-17, 2026-03-18, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
     </row>
@@ -492,12 +492,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
     </row>
@@ -526,12 +526,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-17, 2026-03-18, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
     </row>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BELLATERRA AREIA</t>
+          <t>BELATERRA AREIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BELLATERRA PIETRA</t>
+          <t>BELATERRA PIETRA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BELLATERRA TEMPUS</t>
+          <t>BELATERRA TEMPUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-17, 2026-03-18, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-17, 2026-03-18, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -475,12 +475,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
     </row>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
